--- a/output/pdf_financials_xlsx/PEAK.xlsx
+++ b/output/pdf_financials_xlsx/PEAK.xlsx
@@ -2526,19 +2526,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.338475</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.338475</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.807536</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.366934</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.434223</v>
       </c>
     </row>
     <row r="93">
@@ -4052,7 +4052,11 @@
           <t>Reserve 14</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -4567,7 +4571,11 @@
           <t>Reserve 12</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -4678,7 +4686,11 @@
           <t>Reserve 12</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>1.338475</v>
       </c>

--- a/output/pdf_financials_xlsx/PEAK.xlsx
+++ b/output/pdf_financials_xlsx/PEAK.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.019895</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.114287</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.2687</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.20136</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.030382</v>
       </c>
     </row>
     <row r="13">
@@ -1021,19 +1021,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.523515</v>
+        <v>-1.54341</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.226589</v>
+        <v>-1.340876</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.668482</v>
+        <v>-1.937182</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.409885</v>
+        <v>-2.611245</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.088227</v>
+        <v>-2.118609</v>
       </c>
     </row>
     <row r="28">
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.439356</v>
+        <v>-1.459251</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.159859</v>
+        <v>-1.274146</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.595973</v>
+        <v>-1.864673</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.284088</v>
+        <v>-2.485448</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.042051</v>
+        <v>-2.072433</v>
       </c>
     </row>
     <row r="30">
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>9.217663999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>7.934905</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>6.511177</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.265655</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.452757</v>
       </c>
     </row>
     <row r="35">
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>9.217663999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>7.934905</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>6.511177</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.265655</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.452757</v>
       </c>
     </row>
     <row r="37">
@@ -1488,19 +1488,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9.24653</v>
+        <v>0.028866</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>7.962717</v>
+        <v>0.027812</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.557972</v>
+        <v>0.046795</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.305077</v>
+        <v>0.039422</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.591805</v>
+        <v>0.139048</v>
       </c>
     </row>
     <row r="49">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">

--- a/output/pdf_financials_xlsx/PEAK.xlsx
+++ b/output/pdf_financials_xlsx/PEAK.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.130547</v>
+        <v>0.194362</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.12</v>
+        <v>0.223975</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.132</v>
+        <v>0.252266</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.96994</v>
+        <v>1.129133</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.060554</v>
+        <v>1.218068</v>
       </c>
     </row>
     <row r="8">
@@ -2939,19 +2939,19 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.029402</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.191314</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003606</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004634</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010929</v>
       </c>
     </row>
     <row r="112">
@@ -3461,19 +3461,19 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.029402</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.191314</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003606</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004634</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010929</v>
       </c>
     </row>
     <row r="135">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.388451</v>
+        <v>-1.417853</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.851363</v>
+        <v>-1.862292</v>
       </c>
     </row>
   </sheetData>
@@ -5261,7 +5261,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>-0.029402</v>
       </c>
@@ -5364,7 +5368,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -6989,7 +6997,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>0.063815</v>
       </c>
